--- a/database.xlsx
+++ b/database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\.gemini\antigravity\scratch\inklusi_pintar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Modular\Magang Pensif\Backup IDENTIK - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93B686B-9E25-449C-B71D-2641EE861047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E10620-C0DC-4E69-B0DF-0A4E6F0DF989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="H. Penglihatan" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="203">
   <si>
     <t>IDENTITAS ANAK</t>
   </si>
@@ -242,30 +242,6 @@
     <t>A Diduga</t>
   </si>
   <si>
-    <t>Habiebie Rayyan Suhada</t>
-  </si>
-  <si>
-    <t>Cimahi, 29 Mei 2019</t>
-  </si>
-  <si>
-    <t>Laki-laki</t>
-  </si>
-  <si>
-    <t>PAUD SPS TAAM (sebelumnya)</t>
-  </si>
-  <si>
-    <t>PAUD</t>
-  </si>
-  <si>
-    <t>Jl. Budhi Singkur Mulya RT.003 RW.012 Kelurahan  Pasir Kaliki Kecamatan Cimahi Utara Kota Cimahi</t>
-  </si>
-  <si>
-    <t>Ds. Cibabat Kec. Cimahi Utara Kota Cimahi</t>
-  </si>
-  <si>
-    <t>1. Sindi Ariani, S.Pd  2. Raharja Winata, M.Pd  3. Yopi Yuliana, M.Pd</t>
-  </si>
-  <si>
     <t>IDENTIFIKASI HAMBATAN INTELEKTUAL KATEGORI TUNAGRAHITA</t>
   </si>
   <si>
@@ -288,9 +264,6 @@
   </si>
   <si>
     <t>Perilakunya kurang luwes/fleksibel</t>
-  </si>
-  <si>
-    <t>cukup luwes</t>
   </si>
   <si>
     <t>Pikiran, ingatan, kemauan, dan sifat-sifat mental lainnya sedemikian terbelakang kalau dibandingkan dengan anak normal sebaya</t>
@@ -329,13 +302,7 @@
     <t>Tuliskan temuan lain (jika ada) tentang kondisi anak yang berhubungan dengan hambatan intelektual di bawah ini:</t>
   </si>
   <si>
-    <t>motorik anak cukup bagus, mental belum mandiri (menangis kalau ditinggal Ibunya saat asesmen), kemampuan akademik cukup baik/ringan, ingatan ada beberapa yang ingat dan tidak</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Diduga</t>
-  </si>
-  <si>
-    <t>indikasi tunagrahita ringan</t>
   </si>
   <si>
     <t>IDENTIFIKASI HAMBATAN FISIK MOTORIK</t>
@@ -357,18 +324,6 @@
   </si>
   <si>
     <t>Tuliskan temuan lain (jika ada) tentang kondisi anak yang berhubungan dengan hambatan fisik motorik di bawah ini:</t>
-  </si>
-  <si>
-    <t>Khaisanu Arshad Alsyazani</t>
-  </si>
-  <si>
-    <t>Bandung, 20 November 2019</t>
-  </si>
-  <si>
-    <t>TK Negeri Pembina Kota Cimahi (sebelumnya)</t>
-  </si>
-  <si>
-    <t>TK</t>
   </si>
   <si>
     <t>IDENTIFIKASI HAMBATAN EMOSI KATEGORI TUNALARAS</t>
@@ -410,9 +365,6 @@
     <t>Tuliskan temuan lain (jika ada) tentang kondisi anak yang berhubungan dengan hambatan emosi kategori tunalaras di bawah ini:</t>
   </si>
   <si>
-    <t>Khais</t>
-  </si>
-  <si>
     <t>IDENTIFIKASI HAMBATAN KOMUNIKASI, INTERAKSI, DAN PERILAKU (AUTISM)</t>
   </si>
   <si>
@@ -428,70 +380,37 @@
     <t>Tak dapat bermain dengan teman sebaya</t>
   </si>
   <si>
-    <t>di sekolah sudah aman, lebih akrab di rumah, udah mulai ada d lingkungan tetangga</t>
-  </si>
-  <si>
     <t>Tak ada empati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">belum ada respon, </t>
   </si>
   <si>
     <t>Kurang mampu mengadakan hubungan sosial dan emosional yang timbal balik.</t>
   </si>
   <si>
-    <t>kadang-kadang</t>
-  </si>
-  <si>
     <t>Perkembangan bicara terlambat atau sama sekali tidak berkembang Anak tidak berusaha untuk berkomunikasi secara nonverbal.</t>
-  </si>
-  <si>
-    <t>muali ada bahasa verbal</t>
   </si>
   <si>
     <t>Sering menggunakan bahasa yang aneh dan diulang-ulang.</t>
   </si>
   <si>
-    <t>mengeluarkan bahasa yang di dengar</t>
-  </si>
-  <si>
     <t>Cara bermain yang kurang variatif, kurang imajinatif, dan kuarng dapat meniru.</t>
-  </si>
-  <si>
-    <t>variatif sesuai mainan yang disukai</t>
   </si>
   <si>
     <t>Mempertahankan satu minat atau lebih dengan cara yang sangat khas dan berlebihan.</t>
   </si>
   <si>
-    <t>awalnya senag berenang, dan main air</t>
-  </si>
-  <si>
     <t>Terpaku pada suatu kegiatan yang ritualitastic atau rutinityas yang tak ada gunanya.</t>
-  </si>
-  <si>
-    <t>bermaian sebelum belajar</t>
   </si>
   <si>
     <t>Ada gerakan aneh yang khas dan diulang-ulang.</t>
   </si>
   <si>
-    <t>sekarang sudah jarang, kadang tertawa sendiri/fllaping</t>
-  </si>
-  <si>
     <t>Sering kali sangat terpukau pada bagian-bagian benda.</t>
-  </si>
-  <si>
-    <t>suka dengan benda mobil</t>
   </si>
   <si>
     <t>Tidak suka dipeluk</t>
   </si>
   <si>
     <t>Suka berjalan dengan “jinjit"</t>
-  </si>
-  <si>
-    <t>suka jinjit, jarang pakai alas</t>
   </si>
   <si>
     <t>Tuliskan temuan lain (jika ada) tentang kondisi anak yang berhubungan dengan hambatan komunikasi, interaksi, dan perilaku (autism) di bawah ini:</t>
@@ -1595,44 +1514,65 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1651,27 +1591,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4867,15 +4786,15 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
+      <c r="A15" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="80"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -4927,15 +4846,15 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="76"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="77"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="93"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -4999,7 +4918,7 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="85" t="s">
+      <c r="A19" s="100" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="9">
@@ -5042,7 +4961,7 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="86"/>
+      <c r="A20" s="84"/>
       <c r="B20" s="9">
         <v>2</v>
       </c>
@@ -5083,7 +5002,7 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="9">
         <v>3</v>
       </c>
@@ -5124,7 +5043,7 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="9">
         <v>4</v>
       </c>
@@ -5165,7 +5084,7 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="87"/>
+      <c r="A23" s="85"/>
       <c r="B23" s="9">
         <v>5</v>
       </c>
@@ -5206,7 +5125,7 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="85" t="s">
+      <c r="A24" s="100" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="9">
@@ -5249,7 +5168,7 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="9">
         <v>2</v>
       </c>
@@ -5290,7 +5209,7 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="86"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="9">
         <v>3</v>
       </c>
@@ -5331,7 +5250,7 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="9">
         <v>4</v>
       </c>
@@ -5372,7 +5291,7 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="9">
         <v>5</v>
       </c>
@@ -5413,7 +5332,7 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="86"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="9">
         <v>6</v>
       </c>
@@ -5454,7 +5373,7 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="86"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="9">
         <v>7</v>
       </c>
@@ -5495,7 +5414,7 @@
       <c r="Z30" s="1"/>
     </row>
     <row r="31" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="86"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="9">
         <v>8</v>
       </c>
@@ -5536,7 +5455,7 @@
       <c r="Z31" s="1"/>
     </row>
     <row r="32" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="86"/>
+      <c r="A32" s="84"/>
       <c r="B32" s="9">
         <v>9</v>
       </c>
@@ -5577,7 +5496,7 @@
       <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="86"/>
+      <c r="A33" s="84"/>
       <c r="B33" s="9">
         <v>10</v>
       </c>
@@ -5618,7 +5537,7 @@
       <c r="Z33" s="1"/>
     </row>
     <row r="34" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="86"/>
+      <c r="A34" s="84"/>
       <c r="B34" s="9">
         <v>11</v>
       </c>
@@ -5659,7 +5578,7 @@
       <c r="Z34" s="1"/>
     </row>
     <row r="35" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="86"/>
+      <c r="A35" s="84"/>
       <c r="B35" s="9">
         <v>12</v>
       </c>
@@ -5700,7 +5619,7 @@
       <c r="Z35" s="1"/>
     </row>
     <row r="36" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="87"/>
+      <c r="A36" s="85"/>
       <c r="B36" s="9">
         <v>13</v>
       </c>
@@ -5839,15 +5758,15 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="88" t="s">
+      <c r="A40" s="101" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="79"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="80"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="88"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -5869,13 +5788,13 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="70"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="72"/>
+      <c r="A41" s="89"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="74"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -5897,13 +5816,13 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73"/>
+      <c r="A42" s="90"/>
       <c r="B42" s="69"/>
       <c r="C42" s="69"/>
       <c r="D42" s="69"/>
       <c r="E42" s="69"/>
       <c r="F42" s="69"/>
-      <c r="G42" s="74"/>
+      <c r="G42" s="82"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -5925,13 +5844,13 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="75"/>
-      <c r="B43" s="76"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="77"/>
+      <c r="A43" s="91"/>
+      <c r="B43" s="92"/>
+      <c r="C43" s="92"/>
+      <c r="D43" s="92"/>
+      <c r="E43" s="92"/>
+      <c r="F43" s="92"/>
+      <c r="G43" s="93"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -5953,20 +5872,20 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="89" t="s">
+      <c r="A44" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="71"/>
-      <c r="C44" s="90"/>
+      <c r="B44" s="73"/>
+      <c r="C44" s="95"/>
       <c r="D44" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E44" s="78" t="str">
+      <c r="E44" s="98" t="str">
         <f>IF(G38&lt;100,"Tidak teridentifikasi",IF(G38&gt;=100,"Tunanetra total"))</f>
         <v>Tunanetra total</v>
       </c>
-      <c r="F44" s="79"/>
-      <c r="G44" s="80"/>
+      <c r="F44" s="87"/>
+      <c r="G44" s="88"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -5988,18 +5907,18 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="91"/>
-      <c r="B45" s="92"/>
-      <c r="C45" s="93"/>
+      <c r="A45" s="96"/>
+      <c r="B45" s="76"/>
+      <c r="C45" s="97"/>
       <c r="D45" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E45" s="94" t="str">
+      <c r="E45" s="103" t="str">
         <f>IF(G39&lt;100,"Tidak teridentifikasi",IF(G39&gt;=100,"Low vision"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F45" s="95"/>
-      <c r="G45" s="96"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="105"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -12582,7 +12501,7 @@
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="122" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="B15" s="123"/>
       <c r="C15" s="123"/>
@@ -12603,15 +12522,15 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="76"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="77"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="93"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="64" t="s">
@@ -12630,7 +12549,7 @@
         <v>19</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G18" s="27" t="s">
         <v>50</v>
@@ -12645,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="D19" s="35">
         <v>10</v>
@@ -12662,12 +12581,12 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="86"/>
+      <c r="A20" s="84"/>
       <c r="B20" s="28">
         <v>2</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="D20" s="35">
         <v>10</v>
@@ -12684,12 +12603,12 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="28">
         <v>3</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="D21" s="35">
         <v>10</v>
@@ -12706,12 +12625,12 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="28">
         <v>4</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="D22" s="35">
         <v>10</v>
@@ -12728,12 +12647,12 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="28">
         <v>5</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="D23" s="35">
         <v>10</v>
@@ -12750,12 +12669,12 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="86"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="28">
         <v>6</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="D24" s="35">
         <v>10</v>
@@ -12772,12 +12691,12 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="28">
         <v>7</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="D25" s="35">
         <v>10</v>
@@ -12794,12 +12713,12 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="86"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="28">
         <v>8</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="D26" s="35">
         <v>10</v>
@@ -12816,12 +12735,12 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="28">
         <v>9</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="D27" s="35">
         <v>10</v>
@@ -12838,12 +12757,12 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="28">
         <v>10</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="D28" s="35">
         <v>10</v>
@@ -12860,12 +12779,12 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="86"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="28">
         <v>11</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="D29" s="35">
         <v>10</v>
@@ -12882,12 +12801,12 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="86"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="28">
         <v>12</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="D30" s="35">
         <v>10</v>
@@ -12909,7 +12828,7 @@
         <v>13</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D31" s="35">
         <v>10</v>
@@ -12931,7 +12850,7 @@
         <v>14</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="D32" s="35">
         <v>10</v>
@@ -12953,7 +12872,7 @@
         <v>15</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="D33" s="35">
         <v>10</v>
@@ -12975,7 +12894,7 @@
         <v>16</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="D34" s="35">
         <v>10</v>
@@ -12997,7 +12916,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="D35" s="35">
         <v>10</v>
@@ -13019,7 +12938,7 @@
         <v>18</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="D36" s="35">
         <v>10</v>
@@ -13041,7 +12960,7 @@
         <v>19</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="D37" s="35">
         <v>10</v>
@@ -13063,7 +12982,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="D38" s="35">
         <v>10</v>
@@ -13085,7 +13004,7 @@
         <v>21</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="D39" s="35">
         <v>10</v>
@@ -13107,7 +13026,7 @@
         <v>22</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="D40" s="35">
         <v>10</v>
@@ -13129,7 +13048,7 @@
         <v>23</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="D41" s="35">
         <v>10</v>
@@ -13151,7 +13070,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="D42" s="35">
         <v>10</v>
@@ -13173,7 +13092,7 @@
         <v>25</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="D43" s="35">
         <v>10</v>
@@ -13193,7 +13112,7 @@
       <c r="A44" s="44"/>
       <c r="B44" s="19"/>
       <c r="C44" s="33" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="19"/>
@@ -13205,66 +13124,66 @@
     </row>
     <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="113" t="s">
-        <v>229</v>
-      </c>
-      <c r="B45" s="79"/>
-      <c r="C45" s="79"/>
-      <c r="D45" s="79"/>
-      <c r="E45" s="79"/>
-      <c r="F45" s="79"/>
-      <c r="G45" s="80"/>
+        <v>202</v>
+      </c>
+      <c r="B45" s="87"/>
+      <c r="C45" s="87"/>
+      <c r="D45" s="87"/>
+      <c r="E45" s="87"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="88"/>
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="70"/>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="72"/>
+      <c r="A46" s="89"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="74"/>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="73"/>
+      <c r="A47" s="90"/>
       <c r="B47" s="69"/>
       <c r="C47" s="69"/>
       <c r="D47" s="69"/>
       <c r="E47" s="69"/>
       <c r="F47" s="69"/>
-      <c r="G47" s="74"/>
+      <c r="G47" s="82"/>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="75"/>
-      <c r="B48" s="76"/>
-      <c r="C48" s="76"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="77"/>
+      <c r="A48" s="91"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="92"/>
+      <c r="E48" s="92"/>
+      <c r="F48" s="92"/>
+      <c r="G48" s="93"/>
     </row>
     <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="102" t="s">
+      <c r="A49" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="90"/>
-      <c r="D49" s="103" t="s">
-        <v>95</v>
-      </c>
-      <c r="E49" s="105" t="str">
+      <c r="B49" s="73"/>
+      <c r="C49" s="95"/>
+      <c r="D49" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="E49" s="72" t="str">
         <f>IF(G44&lt;100,"Tidak teridentifikasi",IF(G44&gt;=100,"CERDAS ISTIMEWA"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F49" s="71"/>
-      <c r="G49" s="72"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="74"/>
     </row>
     <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="91"/>
-      <c r="B50" s="92"/>
-      <c r="C50" s="93"/>
-      <c r="D50" s="104"/>
-      <c r="E50" s="106"/>
-      <c r="F50" s="92"/>
-      <c r="G50" s="107"/>
+      <c r="A50" s="96"/>
+      <c r="B50" s="76"/>
+      <c r="C50" s="97"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="77"/>
     </row>
     <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14412,15 +14331,15 @@
       <c r="G13" s="3"/>
     </row>
     <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="97" t="s">
+      <c r="A16" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="83"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="80"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -14434,24 +14353,24 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="77"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="93"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="98"/>
+      <c r="A19" s="107"/>
       <c r="B19" s="69"/>
       <c r="C19" s="69"/>
       <c r="D19" s="69"/>
       <c r="E19" s="69"/>
       <c r="F19" s="69"/>
-      <c r="G19" s="74"/>
+      <c r="G19" s="82"/>
     </row>
     <row r="20" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
@@ -14477,7 +14396,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="108" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="28">
@@ -14501,7 +14420,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="87"/>
+      <c r="A22" s="85"/>
       <c r="B22" s="28">
         <v>2</v>
       </c>
@@ -14523,7 +14442,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="100" t="s">
+      <c r="A23" s="109" t="s">
         <v>54</v>
       </c>
       <c r="B23" s="28">
@@ -14547,7 +14466,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="86"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="28">
         <v>2</v>
       </c>
@@ -14569,7 +14488,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="28">
         <v>3</v>
       </c>
@@ -14591,7 +14510,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="86"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="28">
         <v>4</v>
       </c>
@@ -14613,7 +14532,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="28">
         <v>5</v>
       </c>
@@ -14635,7 +14554,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="28">
         <v>6</v>
       </c>
@@ -14657,7 +14576,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="87"/>
+      <c r="A29" s="85"/>
       <c r="B29" s="28">
         <v>7</v>
       </c>
@@ -14711,78 +14630,78 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="88" t="s">
+      <c r="A32" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="80"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="88"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="70"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="72"/>
+      <c r="A33" s="89"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="73"/>
+      <c r="A34" s="90"/>
       <c r="B34" s="69"/>
       <c r="C34" s="69"/>
       <c r="D34" s="69"/>
       <c r="E34" s="69"/>
       <c r="F34" s="69"/>
-      <c r="G34" s="74"/>
+      <c r="G34" s="82"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="77"/>
+      <c r="A35" s="91"/>
+      <c r="B35" s="92"/>
+      <c r="C35" s="92"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="93"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="71"/>
-      <c r="C36" s="90"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="95"/>
       <c r="D36" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E36" s="78" t="str">
+      <c r="E36" s="98" t="str">
         <f>IF(G30&lt;100,"Tidak teridentifikasi",IF(G30&gt;=100,"Tunarungu berat/menyeluruh"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F36" s="79"/>
-      <c r="G36" s="80"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="88"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="91"/>
-      <c r="B37" s="92"/>
-      <c r="C37" s="93"/>
+      <c r="A37" s="96"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="97"/>
       <c r="D37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="94" t="str">
+      <c r="E37" s="103" t="str">
         <f>IF(G31&lt;100,"Tidak teridentifikasi",IF(G31&gt;=100,"Tunarungu sebagian"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F37" s="95"/>
-      <c r="G37" s="96"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="105"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="101"/>
+      <c r="D38" s="110"/>
       <c r="E38" s="69"/>
       <c r="F38" s="5"/>
       <c r="G38" s="1"/>
@@ -14818,18 +14737,18 @@
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="101"/>
+      <c r="D66" s="110"/>
       <c r="E66" s="69"/>
-      <c r="F66" s="101"/>
+      <c r="F66" s="110"/>
       <c r="G66" s="69"/>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="101"/>
+      <c r="D67" s="110"/>
       <c r="E67" s="69"/>
-      <c r="F67" s="101"/>
+      <c r="F67" s="110"/>
       <c r="G67" s="69"/>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15835,9 +15754,7 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68" t="s">
-        <v>65</v>
-      </c>
+      <c r="C3" s="68"/>
       <c r="D3" s="69"/>
       <c r="E3" s="69"/>
       <c r="F3" s="69"/>
@@ -15850,9 +15767,7 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68" t="s">
-        <v>66</v>
-      </c>
+      <c r="C4" s="68"/>
       <c r="D4" s="69"/>
       <c r="E4" s="69"/>
       <c r="F4" s="69"/>
@@ -15865,9 +15780,7 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68" t="s">
-        <v>67</v>
-      </c>
+      <c r="C5" s="68"/>
       <c r="D5" s="69"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
@@ -15880,9 +15793,7 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68" t="s">
-        <v>68</v>
-      </c>
+      <c r="C6" s="68"/>
       <c r="D6" s="69"/>
       <c r="E6" s="69"/>
       <c r="F6" s="69"/>
@@ -15895,9 +15806,7 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68" t="s">
-        <v>69</v>
-      </c>
+      <c r="C7" s="68"/>
       <c r="D7" s="69"/>
       <c r="E7" s="69"/>
       <c r="F7" s="69"/>
@@ -15910,9 +15819,7 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68" t="s">
-        <v>70</v>
-      </c>
+      <c r="C8" s="68"/>
       <c r="D8" s="69"/>
       <c r="E8" s="69"/>
       <c r="F8" s="69"/>
@@ -15925,9 +15832,7 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68" t="s">
-        <v>71</v>
-      </c>
+      <c r="C9" s="68"/>
       <c r="D9" s="69"/>
       <c r="E9" s="69"/>
       <c r="F9" s="69"/>
@@ -15949,9 +15854,7 @@
       <c r="B11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="3">
-        <v>46191</v>
-      </c>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -15964,9 +15867,7 @@
       <c r="B12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>72</v>
-      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -15995,15 +15896,15 @@
       <c r="G14" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="83"/>
+      <c r="A16" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="80"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -16017,15 +15918,15 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="77"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="93"/>
     </row>
     <row r="19" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
@@ -16044,14 +15945,14 @@
         <v>19</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G19" s="27" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="99" t="str">
+      <c r="A20" s="108" t="str">
         <f>A16</f>
         <v>IDENTIFIKASI HAMBATAN INTELEKTUAL KATEGORI TUNAGRAHITA</v>
       </c>
@@ -16059,7 +15960,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D20" s="35">
         <v>20</v>
@@ -16076,12 +15977,12 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="20">
         <v>2</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D21" s="35">
         <v>20</v>
@@ -16098,12 +15999,12 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="20">
         <v>3</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D22" s="35">
         <v>20</v>
@@ -16120,12 +16021,12 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="20">
         <v>4</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D23" s="35">
         <v>20</v>
@@ -16142,12 +16043,12 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="86"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="20">
         <v>5</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D24" s="35">
         <v>20</v>
@@ -16164,12 +16065,12 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="20">
         <v>6</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D25" s="35">
         <v>20</v>
@@ -16184,17 +16085,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H25" s="38" t="s">
-        <v>81</v>
-      </c>
+      <c r="H25" s="38"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="86"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="20">
         <v>7</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D26" s="35">
         <v>20</v>
@@ -16211,12 +16110,12 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="20">
         <v>8</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D27" s="35">
         <v>5</v>
@@ -16233,12 +16132,12 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="20">
         <v>9</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D28" s="35">
         <v>5</v>
@@ -16255,12 +16154,12 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="86"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="20">
         <v>10</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D29" s="35">
         <v>15</v>
@@ -16277,12 +16176,12 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="86"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="20">
         <v>11</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D30" s="35">
         <v>15</v>
@@ -16299,12 +16198,12 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="86"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="20">
         <v>12</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D31" s="35">
         <v>15</v>
@@ -16321,12 +16220,12 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="86"/>
+      <c r="A32" s="84"/>
       <c r="B32" s="20">
         <v>13</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D32" s="35">
         <v>5</v>
@@ -16343,12 +16242,12 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="86"/>
+      <c r="A33" s="84"/>
       <c r="B33" s="20">
         <v>14</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D33" s="35">
         <v>5</v>
@@ -16365,12 +16264,12 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="86"/>
+      <c r="A34" s="84"/>
       <c r="B34" s="20">
         <v>15</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D34" s="35">
         <v>10</v>
@@ -16387,12 +16286,12 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="87"/>
+      <c r="A35" s="85"/>
       <c r="B35" s="20">
         <v>16</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D35" s="35">
         <v>15</v>
@@ -16412,7 +16311,7 @@
       <c r="A36" s="39"/>
       <c r="B36" s="40"/>
       <c r="C36" s="41" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D36" s="42"/>
       <c r="E36" s="42"/>
@@ -16423,72 +16322,68 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="88" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="80"/>
+      <c r="A37" s="101" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="87"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="87"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="88"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="70" t="s">
-        <v>94</v>
-      </c>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="72"/>
+      <c r="A38" s="89"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="74"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="73"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="69"/>
       <c r="C39" s="69"/>
       <c r="D39" s="69"/>
       <c r="E39" s="69"/>
       <c r="F39" s="69"/>
-      <c r="G39" s="74"/>
+      <c r="G39" s="82"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="75"/>
-      <c r="B40" s="76"/>
-      <c r="C40" s="76"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="77"/>
+      <c r="A40" s="91"/>
+      <c r="B40" s="92"/>
+      <c r="C40" s="92"/>
+      <c r="D40" s="92"/>
+      <c r="E40" s="92"/>
+      <c r="F40" s="92"/>
+      <c r="G40" s="93"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="102" t="s">
+      <c r="A41" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="90"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="95"/>
       <c r="D41" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" s="78" t="str">
+        <v>85</v>
+      </c>
+      <c r="E41" s="98" t="str">
         <f>IF(G36&lt;100,"Tidak teridentifikasi",IF(G36&gt;=100,"Tunagrahita"))</f>
         <v>Tunagrahita</v>
       </c>
-      <c r="F41" s="79"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="38" t="s">
-        <v>96</v>
-      </c>
+      <c r="F41" s="87"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="38"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="91"/>
-      <c r="B42" s="92"/>
-      <c r="C42" s="93"/>
+      <c r="A42" s="96"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="97"/>
       <c r="D42" s="21"/>
-      <c r="E42" s="94"/>
-      <c r="F42" s="95"/>
-      <c r="G42" s="96"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="105"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -17648,15 +17543,15 @@
     </row>
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
+      <c r="A15" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="80"/>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -17670,7 +17565,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="108" t="s">
+      <c r="A17" s="81" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="69"/>
@@ -17678,16 +17573,16 @@
       <c r="D17" s="69"/>
       <c r="E17" s="69"/>
       <c r="F17" s="69"/>
-      <c r="G17" s="74"/>
+      <c r="G17" s="82"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
       <c r="B18" s="1"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="101"/>
+      <c r="D18" s="110"/>
       <c r="E18" s="69"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="74"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="82"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
@@ -17713,7 +17608,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="99" t="str">
+      <c r="A20" s="108" t="str">
         <f>A15</f>
         <v>IDENTIFIKASI HAMBATAN FISIK MOTORIK</v>
       </c>
@@ -17721,7 +17616,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D20" s="35">
         <v>100</v>
@@ -17738,12 +17633,12 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="28">
         <v>2</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D21" s="35">
         <v>100</v>
@@ -17760,12 +17655,12 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D22" s="35">
         <v>100</v>
@@ -17782,12 +17677,12 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="28">
         <v>4</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D23" s="35">
         <v>100</v>
@@ -17804,12 +17699,12 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="87"/>
+      <c r="A24" s="85"/>
       <c r="B24" s="28">
         <v>5</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D24" s="35">
         <v>100</v>
@@ -17829,7 +17724,7 @@
       <c r="A25" s="39"/>
       <c r="B25" s="40"/>
       <c r="C25" s="41" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D25" s="42"/>
       <c r="E25" s="42"/>
@@ -17840,67 +17735,67 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="88" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="80"/>
+      <c r="A26" s="101" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="88"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="70"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="72"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="74"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="73"/>
+      <c r="A28" s="90"/>
       <c r="B28" s="69"/>
       <c r="C28" s="69"/>
       <c r="D28" s="69"/>
       <c r="E28" s="69"/>
       <c r="F28" s="69"/>
-      <c r="G28" s="74"/>
+      <c r="G28" s="82"/>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="75"/>
-      <c r="B29" s="76"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="77"/>
+      <c r="A29" s="91"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="93"/>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="102" t="s">
+      <c r="A30" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="71"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="103" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="105" t="str">
+      <c r="B30" s="73"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="72" t="str">
         <f>IF(G25&lt;100,"Tidak teridentifikasi",IF(G25&gt;=100,"Tunadaksa"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F30" s="71"/>
-      <c r="G30" s="72"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="74"/>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="91"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="104"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="107"/>
+      <c r="A31" s="96"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="97"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="77"/>
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -18939,9 +18834,7 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68" t="s">
-        <v>104</v>
-      </c>
+      <c r="C3" s="68"/>
       <c r="D3" s="69"/>
       <c r="E3" s="69"/>
       <c r="F3" s="69"/>
@@ -18954,9 +18847,7 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68" t="s">
-        <v>105</v>
-      </c>
+      <c r="C4" s="68"/>
       <c r="D4" s="69"/>
       <c r="E4" s="69"/>
       <c r="F4" s="69"/>
@@ -18969,9 +18860,7 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68" t="s">
-        <v>67</v>
-      </c>
+      <c r="C5" s="68"/>
       <c r="D5" s="69"/>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
@@ -18984,9 +18873,7 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68" t="s">
-        <v>106</v>
-      </c>
+      <c r="C6" s="68"/>
       <c r="D6" s="69"/>
       <c r="E6" s="69"/>
       <c r="F6" s="69"/>
@@ -18999,9 +18886,7 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68" t="s">
-        <v>107</v>
-      </c>
+      <c r="C7" s="68"/>
       <c r="D7" s="69"/>
       <c r="E7" s="69"/>
       <c r="F7" s="69"/>
@@ -19083,15 +18968,15 @@
     </row>
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
+      <c r="A15" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="80"/>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -19105,7 +18990,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="108" t="s">
+      <c r="A17" s="81" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="69"/>
@@ -19113,7 +18998,7 @@
       <c r="D17" s="69"/>
       <c r="E17" s="69"/>
       <c r="F17" s="69"/>
-      <c r="G17" s="74"/>
+      <c r="G17" s="82"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
@@ -19126,7 +19011,7 @@
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="51" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>16</v>
@@ -19148,14 +19033,14 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="109" t="s">
-        <v>110</v>
+      <c r="A20" s="83" t="s">
+        <v>95</v>
       </c>
       <c r="B20" s="28">
         <v>1</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D20" s="35">
         <v>50</v>
@@ -19172,12 +19057,12 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="28">
         <v>2</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D21" s="35">
         <v>40</v>
@@ -19194,12 +19079,12 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D22" s="35">
         <v>20</v>
@@ -19216,12 +19101,12 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="28">
         <v>4</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D23" s="35">
         <v>20</v>
@@ -19238,12 +19123,12 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="86"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="28">
         <v>5</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D24" s="35">
         <v>30</v>
@@ -19260,12 +19145,12 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="28">
         <v>6</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D25" s="35">
         <v>50</v>
@@ -19282,12 +19167,12 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="86"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="28">
         <v>7</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D26" s="35">
         <v>20</v>
@@ -19304,12 +19189,12 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="28">
         <v>8</v>
       </c>
       <c r="C27" s="52" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D27" s="35">
         <v>30</v>
@@ -19326,12 +19211,12 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="28">
         <v>9</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D28" s="35">
         <v>50</v>
@@ -19348,10 +19233,10 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="87"/>
+      <c r="A29" s="85"/>
       <c r="B29" s="53"/>
       <c r="C29" s="54" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D29" s="53"/>
       <c r="E29" s="53"/>
@@ -19362,67 +19247,67 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="110" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="80"/>
+      <c r="A30" s="86" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="88"/>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="70"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="72"/>
+      <c r="A31" s="89"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="74"/>
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="73"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="69"/>
       <c r="C32" s="69"/>
       <c r="D32" s="69"/>
       <c r="E32" s="69"/>
       <c r="F32" s="69"/>
-      <c r="G32" s="74"/>
+      <c r="G32" s="82"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="75"/>
-      <c r="B33" s="76"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="77"/>
+      <c r="A33" s="91"/>
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="93"/>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="102" t="s">
+      <c r="A34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="71"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="103" t="s">
-        <v>95</v>
-      </c>
-      <c r="E34" s="105" t="str">
+      <c r="B34" s="73"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="72" t="str">
         <f>IF(G29&lt;100,"Tidak teridentifikasi",IF(G29&gt;=100,"Tunalaras"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F34" s="71"/>
-      <c r="G34" s="72"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="74"/>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="91"/>
-      <c r="B35" s="92"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="104"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="107"/>
+      <c r="A35" s="96"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="97"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="77"/>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20455,9 +20340,7 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68" t="s">
-        <v>121</v>
-      </c>
+      <c r="C3" s="68"/>
       <c r="D3" s="69"/>
       <c r="E3" s="69"/>
       <c r="F3" s="69"/>
@@ -20591,15 +20474,15 @@
     </row>
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
-        <v>122</v>
-      </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
+      <c r="A15" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="80"/>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -20613,7 +20496,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="108" t="s">
+      <c r="A17" s="81" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="69"/>
@@ -20621,7 +20504,7 @@
       <c r="D17" s="69"/>
       <c r="E17" s="69"/>
       <c r="F17" s="69"/>
-      <c r="G17" s="74"/>
+      <c r="G17" s="82"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
@@ -20649,21 +20532,21 @@
         <v>19</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="G19" s="27" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="109" t="s">
-        <v>124</v>
+      <c r="A20" s="83" t="s">
+        <v>108</v>
       </c>
       <c r="B20" s="28">
         <v>1</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D20" s="35">
         <v>20</v>
@@ -20680,12 +20563,12 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="28">
         <v>2</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D21" s="35">
         <v>10</v>
@@ -20700,17 +20583,15 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H21" s="38" t="s">
-        <v>127</v>
-      </c>
+      <c r="H21" s="38"/>
     </row>
     <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D22" s="35">
         <v>10</v>
@@ -20725,17 +20606,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H22" s="38" t="s">
-        <v>129</v>
-      </c>
+      <c r="H22" s="38"/>
     </row>
     <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="28">
         <v>4</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="D23" s="35">
         <v>20</v>
@@ -20750,17 +20629,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H23" s="38" t="s">
-        <v>131</v>
-      </c>
+      <c r="H23" s="38"/>
     </row>
     <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="86"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="28">
         <v>5</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D24" s="35">
         <v>10</v>
@@ -20775,17 +20652,15 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H24" s="38" t="s">
-        <v>133</v>
-      </c>
+      <c r="H24" s="38"/>
     </row>
     <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="28">
         <v>6</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="D25" s="35">
         <v>20</v>
@@ -20800,17 +20675,15 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H25" s="38" t="s">
-        <v>135</v>
-      </c>
+      <c r="H25" s="38"/>
     </row>
     <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="86"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="28">
         <v>7</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="D26" s="35">
         <v>10</v>
@@ -20825,17 +20698,15 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H26" s="38" t="s">
-        <v>137</v>
-      </c>
+      <c r="H26" s="38"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="28">
         <v>8</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="D27" s="35">
         <v>10</v>
@@ -20850,17 +20721,15 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H27" s="38" t="s">
-        <v>139</v>
-      </c>
+      <c r="H27" s="38"/>
     </row>
     <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="28">
         <v>9</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="D28" s="35">
         <v>20</v>
@@ -20875,17 +20744,15 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H28" s="38" t="s">
-        <v>141</v>
-      </c>
+      <c r="H28" s="38"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="86"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="28">
         <v>10</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="D29" s="35">
         <v>20</v>
@@ -20900,17 +20767,15 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H29" s="38" t="s">
-        <v>143</v>
-      </c>
+      <c r="H29" s="38"/>
     </row>
     <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="86"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="28">
         <v>11</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="D30" s="35">
         <v>10</v>
@@ -20925,17 +20790,15 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H30" s="38" t="s">
-        <v>145</v>
-      </c>
+      <c r="H30" s="38"/>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="86"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="28">
         <v>12</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="D31" s="35">
         <v>20</v>
@@ -20952,12 +20815,12 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="87"/>
+      <c r="A32" s="85"/>
       <c r="B32" s="28">
         <v>13</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="D32" s="35">
         <v>10</v>
@@ -20972,15 +20835,13 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H32" s="38" t="s">
-        <v>148</v>
-      </c>
+      <c r="H32" s="38"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18"/>
       <c r="B33" s="19"/>
       <c r="C33" s="33" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
@@ -20992,66 +20853,66 @@
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="113" t="s">
-        <v>149</v>
-      </c>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="80"/>
+        <v>122</v>
+      </c>
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="88"/>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="70"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="72"/>
+      <c r="A35" s="89"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="74"/>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="73"/>
+      <c r="A36" s="90"/>
       <c r="B36" s="69"/>
       <c r="C36" s="69"/>
       <c r="D36" s="69"/>
       <c r="E36" s="69"/>
       <c r="F36" s="69"/>
-      <c r="G36" s="74"/>
+      <c r="G36" s="82"/>
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="75"/>
-      <c r="B37" s="76"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="77"/>
+      <c r="A37" s="91"/>
+      <c r="B37" s="92"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="93"/>
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="102" t="s">
+      <c r="A38" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="71"/>
-      <c r="C38" s="90"/>
-      <c r="D38" s="103" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="105" t="str">
+      <c r="B38" s="73"/>
+      <c r="C38" s="95"/>
+      <c r="D38" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="E38" s="72" t="str">
         <f>IF(G33&lt;100,"Tidak teridentifikasi",IF(G33&gt;=100,"AUTIS"))</f>
         <v>AUTIS</v>
       </c>
-      <c r="F38" s="71"/>
-      <c r="G38" s="72"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="74"/>
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="75"/>
-      <c r="B39" s="76"/>
+      <c r="A39" s="91"/>
+      <c r="B39" s="92"/>
       <c r="C39" s="114"/>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="77"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="93"/>
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22216,14 +22077,14 @@
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="115" t="s">
-        <v>150</v>
-      </c>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="83"/>
+        <v>123</v>
+      </c>
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="80"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -22237,7 +22098,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="108" t="s">
+      <c r="A18" s="81" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="69"/>
@@ -22245,7 +22106,7 @@
       <c r="D18" s="69"/>
       <c r="E18" s="69"/>
       <c r="F18" s="69"/>
-      <c r="G18" s="74"/>
+      <c r="G18" s="82"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
@@ -22273,7 +22134,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="G20" s="59" t="s">
         <v>50</v>
@@ -22281,13 +22142,13 @@
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="116" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="B21" s="28">
         <v>1</v>
       </c>
       <c r="C21" s="60" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="D21" s="35">
         <v>10</v>
@@ -22304,12 +22165,12 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="73"/>
+      <c r="A22" s="90"/>
       <c r="B22" s="28">
         <v>2</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="D22" s="35">
         <v>17</v>
@@ -22326,12 +22187,12 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73"/>
+      <c r="A23" s="90"/>
       <c r="B23" s="28">
         <v>3</v>
       </c>
       <c r="C23" s="60" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="D23" s="35">
         <v>17</v>
@@ -22348,12 +22209,12 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="73"/>
+      <c r="A24" s="90"/>
       <c r="B24" s="28">
         <v>4</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="D24" s="35">
         <v>17</v>
@@ -22370,12 +22231,12 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="73"/>
+      <c r="A25" s="90"/>
       <c r="B25" s="28">
         <v>5</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D25" s="35">
         <v>17</v>
@@ -22392,12 +22253,12 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="73"/>
+      <c r="A26" s="90"/>
       <c r="B26" s="28">
         <v>6</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="D26" s="35">
         <v>17</v>
@@ -22414,12 +22275,12 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="73"/>
+      <c r="A27" s="90"/>
       <c r="B27" s="28">
         <v>7</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="D27" s="35">
         <v>17</v>
@@ -22436,12 +22297,12 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="73"/>
+      <c r="A28" s="90"/>
       <c r="B28" s="28">
         <v>8</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="D28" s="35">
         <v>17</v>
@@ -22458,12 +22319,12 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="73"/>
+      <c r="A29" s="90"/>
       <c r="B29" s="28">
         <v>9</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="D29" s="35">
         <v>17</v>
@@ -22480,12 +22341,12 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="73"/>
+      <c r="A30" s="90"/>
       <c r="B30" s="28">
         <v>10</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="D30" s="35">
         <v>17</v>
@@ -22502,12 +22363,12 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="73"/>
+      <c r="A31" s="90"/>
       <c r="B31" s="28">
         <v>11</v>
       </c>
       <c r="C31" s="60" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="D31" s="35">
         <v>17</v>
@@ -22524,12 +22385,12 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="73"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="28">
         <v>12</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="D32" s="35">
         <v>17</v>
@@ -22546,12 +22407,12 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="73"/>
+      <c r="A33" s="90"/>
       <c r="B33" s="28">
         <v>13</v>
       </c>
       <c r="C33" s="60" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="D33" s="35">
         <v>17</v>
@@ -22568,12 +22429,12 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="73"/>
+      <c r="A34" s="90"/>
       <c r="B34" s="28">
         <v>14</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D34" s="35">
         <v>17</v>
@@ -22590,12 +22451,12 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="73"/>
+      <c r="A35" s="90"/>
       <c r="B35" s="28">
         <v>15</v>
       </c>
       <c r="C35" s="60" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D35" s="35">
         <v>17</v>
@@ -22612,12 +22473,12 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="73"/>
+      <c r="A36" s="90"/>
       <c r="B36" s="28">
         <v>16</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="D36" s="35">
         <v>17</v>
@@ -22634,12 +22495,12 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="73"/>
+      <c r="A37" s="90"/>
       <c r="B37" s="28">
         <v>17</v>
       </c>
       <c r="C37" s="60" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="D37" s="35">
         <v>17</v>
@@ -22656,12 +22517,12 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="73"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="28">
         <v>18</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="D38" s="35">
         <v>17</v>
@@ -22681,7 +22542,7 @@
       <c r="A39" s="44"/>
       <c r="B39" s="1"/>
       <c r="C39" s="41" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D39" s="40"/>
       <c r="E39" s="40"/>
@@ -22693,66 +22554,66 @@
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="113" t="s">
-        <v>171</v>
-      </c>
-      <c r="B40" s="79"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="80"/>
+        <v>144</v>
+      </c>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="88"/>
     </row>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="70"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="72"/>
+      <c r="A41" s="89"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73"/>
+      <c r="A42" s="90"/>
       <c r="B42" s="69"/>
       <c r="C42" s="69"/>
       <c r="D42" s="69"/>
       <c r="E42" s="69"/>
       <c r="F42" s="69"/>
-      <c r="G42" s="74"/>
+      <c r="G42" s="82"/>
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="75"/>
-      <c r="B43" s="76"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="77"/>
+      <c r="A43" s="91"/>
+      <c r="B43" s="92"/>
+      <c r="C43" s="92"/>
+      <c r="D43" s="92"/>
+      <c r="E43" s="92"/>
+      <c r="F43" s="92"/>
+      <c r="G43" s="93"/>
     </row>
     <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="102" t="s">
+      <c r="A44" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="71"/>
-      <c r="C44" s="90"/>
-      <c r="D44" s="103" t="s">
-        <v>95</v>
-      </c>
-      <c r="E44" s="105" t="str">
+      <c r="B44" s="73"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="E44" s="72" t="str">
         <f>IF(G39&lt;100,"Tidak teridentifikasi",IF(G39&gt;=100,"ADHD/HIPERAKTIF"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F44" s="71"/>
-      <c r="G44" s="72"/>
+      <c r="F44" s="73"/>
+      <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="91"/>
-      <c r="B45" s="92"/>
-      <c r="C45" s="93"/>
-      <c r="D45" s="104"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="92"/>
-      <c r="G45" s="107"/>
+      <c r="A45" s="96"/>
+      <c r="B45" s="76"/>
+      <c r="C45" s="97"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="75"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="77"/>
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -23910,15 +23771,15 @@
     </row>
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
-        <v>172</v>
-      </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
+      <c r="A15" s="78" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="80"/>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="44"/>
@@ -23941,15 +23802,15 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="77"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="93"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
@@ -23983,7 +23844,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="D20" s="9">
         <v>20</v>
@@ -24005,7 +23866,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="D21" s="9">
         <v>30</v>
@@ -24027,7 +23888,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="D22" s="9">
         <v>30</v>
@@ -24049,7 +23910,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D23" s="9">
         <v>30</v>
@@ -24071,7 +23932,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="D24" s="9">
         <v>30</v>
@@ -24093,7 +23954,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="D25" s="9">
         <v>30</v>
@@ -24115,7 +23976,7 @@
         <v>7</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="D26" s="9">
         <v>30</v>
@@ -24137,7 +23998,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D27" s="9">
         <v>30</v>
@@ -24159,7 +24020,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="D28" s="9">
         <v>30</v>
@@ -24181,7 +24042,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="61" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="D29" s="9">
         <v>30</v>
@@ -24201,7 +24062,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="19"/>
       <c r="C30" s="33" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
@@ -24213,66 +24074,66 @@
     </row>
     <row r="31" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="119" t="s">
-        <v>183</v>
-      </c>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="80"/>
+        <v>156</v>
+      </c>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="88"/>
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="70"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="72"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="74"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="73"/>
+      <c r="A33" s="90"/>
       <c r="B33" s="69"/>
       <c r="C33" s="69"/>
       <c r="D33" s="69"/>
       <c r="E33" s="69"/>
       <c r="F33" s="69"/>
-      <c r="G33" s="74"/>
+      <c r="G33" s="82"/>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
-      <c r="B34" s="76"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="77"/>
+      <c r="A34" s="91"/>
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="93"/>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="102" t="s">
+      <c r="A35" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="90"/>
-      <c r="D35" s="103" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" s="105" t="str">
+      <c r="B35" s="73"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="72" t="str">
         <f>IF(G30&lt;100,"Tidak teridentifikasi",IF(G30&gt;=100,"SLOW LEARNER/LAMBAN BELAJAR"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F35" s="71"/>
-      <c r="G35" s="72"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="74"/>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="91"/>
-      <c r="B36" s="92"/>
-      <c r="C36" s="93"/>
-      <c r="D36" s="104"/>
-      <c r="E36" s="106"/>
-      <c r="F36" s="92"/>
-      <c r="G36" s="107"/>
+      <c r="A36" s="96"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="97"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="77"/>
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -25447,15 +25308,15 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
-        <v>184</v>
-      </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
+      <c r="A15" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="80"/>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -25469,7 +25330,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="108" t="s">
+      <c r="A17" s="81" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="69"/>
@@ -25477,16 +25338,16 @@
       <c r="D17" s="69"/>
       <c r="E17" s="69"/>
       <c r="F17" s="69"/>
-      <c r="G17" s="74"/>
+      <c r="G17" s="82"/>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="84"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="77"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="93"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="51" t="s">
@@ -25512,14 +25373,14 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="85" t="s">
-        <v>185</v>
+      <c r="A20" s="100" t="s">
+        <v>158</v>
       </c>
       <c r="B20" s="28">
         <v>1</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D20" s="35">
         <v>50</v>
@@ -25536,12 +25397,12 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="28">
         <v>2</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="D21" s="35">
         <v>50</v>
@@ -25558,12 +25419,12 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="87"/>
+      <c r="A22" s="85"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="D22" s="35">
         <v>50</v>
@@ -25580,14 +25441,14 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="85" t="s">
-        <v>189</v>
+      <c r="A23" s="100" t="s">
+        <v>162</v>
       </c>
       <c r="B23" s="28">
         <v>1</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="D23" s="35">
         <v>50</v>
@@ -25604,12 +25465,12 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="86"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="28">
         <v>2</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="D24" s="35">
         <v>50</v>
@@ -25626,12 +25487,12 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="28">
         <v>3</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="D25" s="35">
         <v>50</v>
@@ -25648,12 +25509,12 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="87"/>
+      <c r="A26" s="85"/>
       <c r="B26" s="28">
         <v>4</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="D26" s="35">
         <v>50</v>
@@ -25671,13 +25532,13 @@
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="121" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="B27" s="28">
         <v>1</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="D27" s="35">
         <v>50</v>
@@ -25694,12 +25555,12 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="28">
         <v>2</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="D28" s="35">
         <v>50</v>
@@ -25716,12 +25577,12 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="86"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="28">
         <v>3</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="D29" s="35">
         <v>50</v>
@@ -25738,12 +25599,12 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="86"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="28">
         <v>4</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="D30" s="35">
         <v>50</v>
@@ -25760,12 +25621,12 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="87"/>
+      <c r="A31" s="85"/>
       <c r="B31" s="28">
         <v>5</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="D31" s="35">
         <v>50</v>
@@ -25783,41 +25644,41 @@
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="113" t="s">
-        <v>200</v>
-      </c>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="80"/>
+        <v>173</v>
+      </c>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="88"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="70"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="72"/>
+      <c r="A33" s="89"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="73"/>
+      <c r="A34" s="90"/>
       <c r="B34" s="69"/>
       <c r="C34" s="69"/>
       <c r="D34" s="69"/>
       <c r="E34" s="69"/>
       <c r="F34" s="69"/>
-      <c r="G34" s="74"/>
+      <c r="G34" s="82"/>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="77"/>
+      <c r="A35" s="91"/>
+      <c r="B35" s="92"/>
+      <c r="C35" s="92"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="93"/>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44"/>
@@ -25851,7 +25712,7 @@
       <c r="A38" s="44"/>
       <c r="B38" s="1"/>
       <c r="C38" s="17" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
@@ -25862,48 +25723,48 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="102" t="s">
+      <c r="A39" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="90"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="95"/>
       <c r="D39" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E39" s="78" t="str">
+      <c r="E39" s="98" t="str">
         <f>IF(G36&lt;100,"Tidak teridentifikasi",IF(G36&gt;=100,"DISKLEKSIA"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F39" s="79"/>
-      <c r="G39" s="80"/>
+      <c r="F39" s="87"/>
+      <c r="G39" s="88"/>
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="73"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="69"/>
       <c r="C40" s="120"/>
       <c r="D40" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="78" t="str">
+      <c r="E40" s="98" t="str">
         <f>IF(G37&lt;100,"Tidak teridentifikasi",IF(G37&gt;=100,"DISGRAFIA"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F40" s="79"/>
-      <c r="G40" s="80"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="88"/>
     </row>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="91"/>
-      <c r="B41" s="92"/>
-      <c r="C41" s="93"/>
+      <c r="A41" s="96"/>
+      <c r="B41" s="76"/>
+      <c r="C41" s="97"/>
       <c r="D41" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="E41" s="94" t="str">
+        <v>175</v>
+      </c>
+      <c r="E41" s="103" t="str">
         <f>IF(G38&lt;100,"Tidak teridentifikasi",IF(G38&gt;=100,"DISKALKULIA"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F41" s="95"/>
-      <c r="G41" s="96"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="105"/>
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Modular\Magang Pensif\Backup IDENTIK - Copy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E10620-C0DC-4E69-B0DF-0A4E6F0DF989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16302F2B-76AC-4714-BA78-09AE0A21FD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="H. Penglihatan" sheetId="1" r:id="rId1"/>
@@ -374,9 +374,6 @@
     <t>AUTIS</t>
   </si>
   <si>
-    <t>Tidak mau kontrak mata, ekspresi muka kurang hidup, gerak-gerik kurang tertuju</t>
-  </si>
-  <si>
     <t>Tak dapat bermain dengan teman sebaya</t>
   </si>
   <si>
@@ -396,9 +393,6 @@
   </si>
   <si>
     <t>Mempertahankan satu minat atau lebih dengan cara yang sangat khas dan berlebihan.</t>
-  </si>
-  <si>
-    <t>Terpaku pada suatu kegiatan yang ritualitastic atau rutinityas yang tak ada gunanya.</t>
   </si>
   <si>
     <t>Ada gerakan aneh yang khas dan diulang-ulang.</t>
@@ -678,6 +672,12 @@
   </si>
   <si>
     <t>Tuliskan temuan lain (jika ada) tentang kondisi anak yang berhubungan dengan cerdas istimewa di bawah ini:</t>
+  </si>
+  <si>
+    <t>Tidak mau kontak mata, ekspresi muka kurang hidup, gerak-gerik kurang tertuju</t>
+  </si>
+  <si>
+    <t>Terpaku pada suatu kegiatan yang ritualitastic atau rutinitas yang tak ada gunanya.</t>
   </si>
 </sst>
 </file>
@@ -1505,82 +1505,58 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1591,6 +1567,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4352,15 +4352,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -4416,11 +4416,11 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -4448,11 +4448,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -4480,11 +4480,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -4512,11 +4512,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -4544,11 +4544,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -4576,11 +4576,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -4608,11 +4608,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -4846,15 +4846,15 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="92"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="93"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="74"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -4918,7 +4918,7 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="100" t="s">
+      <c r="A19" s="82" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="9">
@@ -4961,7 +4961,7 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="84"/>
+      <c r="A20" s="83"/>
       <c r="B20" s="9">
         <v>2</v>
       </c>
@@ -5002,7 +5002,7 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="9">
         <v>3</v>
       </c>
@@ -5043,7 +5043,7 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
+      <c r="A22" s="83"/>
       <c r="B22" s="9">
         <v>4</v>
       </c>
@@ -5084,7 +5084,7 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="9">
         <v>5</v>
       </c>
@@ -5125,7 +5125,7 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="100" t="s">
+      <c r="A24" s="82" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="9">
@@ -5168,7 +5168,7 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="9">
         <v>2</v>
       </c>
@@ -5209,7 +5209,7 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
+      <c r="A26" s="83"/>
       <c r="B26" s="9">
         <v>3</v>
       </c>
@@ -5250,7 +5250,7 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
+      <c r="A27" s="83"/>
       <c r="B27" s="9">
         <v>4</v>
       </c>
@@ -5291,7 +5291,7 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="9">
         <v>5</v>
       </c>
@@ -5332,7 +5332,7 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
+      <c r="A29" s="83"/>
       <c r="B29" s="9">
         <v>6</v>
       </c>
@@ -5373,7 +5373,7 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
+      <c r="A30" s="83"/>
       <c r="B30" s="9">
         <v>7</v>
       </c>
@@ -5414,7 +5414,7 @@
       <c r="Z30" s="1"/>
     </row>
     <row r="31" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="84"/>
+      <c r="A31" s="83"/>
       <c r="B31" s="9">
         <v>8</v>
       </c>
@@ -5455,7 +5455,7 @@
       <c r="Z31" s="1"/>
     </row>
     <row r="32" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="84"/>
+      <c r="A32" s="83"/>
       <c r="B32" s="9">
         <v>9</v>
       </c>
@@ -5496,7 +5496,7 @@
       <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="84"/>
+      <c r="A33" s="83"/>
       <c r="B33" s="9">
         <v>10</v>
       </c>
@@ -5537,7 +5537,7 @@
       <c r="Z33" s="1"/>
     </row>
     <row r="34" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="84"/>
+      <c r="A34" s="83"/>
       <c r="B34" s="9">
         <v>11</v>
       </c>
@@ -5578,7 +5578,7 @@
       <c r="Z34" s="1"/>
     </row>
     <row r="35" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="84"/>
+      <c r="A35" s="83"/>
       <c r="B35" s="9">
         <v>12</v>
       </c>
@@ -5619,7 +5619,7 @@
       <c r="Z35" s="1"/>
     </row>
     <row r="36" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
+      <c r="A36" s="84"/>
       <c r="B36" s="9">
         <v>13</v>
       </c>
@@ -5758,15 +5758,15 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="101" t="s">
+      <c r="A40" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="87"/>
-      <c r="G40" s="88"/>
+      <c r="B40" s="76"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="77"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -5788,13 +5788,13 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="89"/>
-      <c r="B41" s="73"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="74"/>
+      <c r="A41" s="67"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="69"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -5816,13 +5816,13 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="90"/>
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="82"/>
+      <c r="A42" s="70"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="71"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -5844,13 +5844,13 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="91"/>
-      <c r="B43" s="92"/>
-      <c r="C43" s="92"/>
-      <c r="D43" s="92"/>
-      <c r="E43" s="92"/>
-      <c r="F43" s="92"/>
-      <c r="G43" s="93"/>
+      <c r="A43" s="72"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="73"/>
+      <c r="G43" s="74"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -5872,20 +5872,20 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="102" t="s">
+      <c r="A44" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="73"/>
-      <c r="C44" s="95"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="87"/>
       <c r="D44" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E44" s="98" t="str">
+      <c r="E44" s="75" t="str">
         <f>IF(G38&lt;100,"Tidak teridentifikasi",IF(G38&gt;=100,"Tunanetra total"))</f>
         <v>Tunanetra total</v>
       </c>
-      <c r="F44" s="87"/>
-      <c r="G44" s="88"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="77"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -5907,18 +5907,18 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="96"/>
-      <c r="B45" s="76"/>
-      <c r="C45" s="97"/>
+      <c r="A45" s="88"/>
+      <c r="B45" s="89"/>
+      <c r="C45" s="90"/>
       <c r="D45" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E45" s="103" t="str">
+      <c r="E45" s="91" t="str">
         <f>IF(G39&lt;100,"Tidak teridentifikasi",IF(G39&gt;=100,"Low vision"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F45" s="104"/>
-      <c r="G45" s="105"/>
+      <c r="F45" s="92"/>
+      <c r="G45" s="93"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -12296,6 +12296,11 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A41:G43"/>
@@ -12308,11 +12313,6 @@
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A44:C45"/>
     <mergeCell ref="E45:G45"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <printOptions gridLines="1"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0" footer="0"/>
@@ -12340,15 +12340,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -12366,11 +12366,11 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -12379,11 +12379,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -12392,11 +12392,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -12405,11 +12405,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -12418,11 +12418,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -12431,11 +12431,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -12444,11 +12444,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -12501,7 +12501,7 @@
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="122" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B15" s="123"/>
       <c r="C15" s="123"/>
@@ -12522,15 +12522,15 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="92"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="93"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="74"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="64" t="s">
@@ -12564,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D19" s="35">
         <v>10</v>
@@ -12581,12 +12581,12 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="84"/>
+      <c r="A20" s="83"/>
       <c r="B20" s="28">
         <v>2</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D20" s="35">
         <v>10</v>
@@ -12603,12 +12603,12 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="28">
         <v>3</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D21" s="35">
         <v>10</v>
@@ -12625,12 +12625,12 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
+      <c r="A22" s="83"/>
       <c r="B22" s="28">
         <v>4</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D22" s="35">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="28">
         <v>5</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D23" s="35">
         <v>10</v>
@@ -12669,12 +12669,12 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
+      <c r="A24" s="83"/>
       <c r="B24" s="28">
         <v>6</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D24" s="35">
         <v>10</v>
@@ -12691,12 +12691,12 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="28">
         <v>7</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D25" s="35">
         <v>10</v>
@@ -12713,12 +12713,12 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
+      <c r="A26" s="83"/>
       <c r="B26" s="28">
         <v>8</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D26" s="35">
         <v>10</v>
@@ -12735,12 +12735,12 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
+      <c r="A27" s="83"/>
       <c r="B27" s="28">
         <v>9</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D27" s="35">
         <v>10</v>
@@ -12757,12 +12757,12 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="28">
         <v>10</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D28" s="35">
         <v>10</v>
@@ -12779,12 +12779,12 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
+      <c r="A29" s="83"/>
       <c r="B29" s="28">
         <v>11</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D29" s="35">
         <v>10</v>
@@ -12801,12 +12801,12 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
+      <c r="A30" s="83"/>
       <c r="B30" s="28">
         <v>12</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D30" s="35">
         <v>10</v>
@@ -12828,7 +12828,7 @@
         <v>13</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D31" s="35">
         <v>10</v>
@@ -12850,7 +12850,7 @@
         <v>14</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D32" s="35">
         <v>10</v>
@@ -12872,7 +12872,7 @@
         <v>15</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D33" s="35">
         <v>10</v>
@@ -12894,7 +12894,7 @@
         <v>16</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D34" s="35">
         <v>10</v>
@@ -12916,7 +12916,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D35" s="35">
         <v>10</v>
@@ -12938,7 +12938,7 @@
         <v>18</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D36" s="35">
         <v>10</v>
@@ -12960,7 +12960,7 @@
         <v>19</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D37" s="35">
         <v>10</v>
@@ -12982,7 +12982,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D38" s="35">
         <v>10</v>
@@ -13004,7 +13004,7 @@
         <v>21</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D39" s="35">
         <v>10</v>
@@ -13026,7 +13026,7 @@
         <v>22</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D40" s="35">
         <v>10</v>
@@ -13048,7 +13048,7 @@
         <v>23</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D41" s="35">
         <v>10</v>
@@ -13070,7 +13070,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D42" s="35">
         <v>10</v>
@@ -13092,7 +13092,7 @@
         <v>25</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D43" s="35">
         <v>10</v>
@@ -13124,66 +13124,66 @@
     </row>
     <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="113" t="s">
-        <v>202</v>
-      </c>
-      <c r="B45" s="87"/>
-      <c r="C45" s="87"/>
-      <c r="D45" s="87"/>
-      <c r="E45" s="87"/>
-      <c r="F45" s="87"/>
-      <c r="G45" s="88"/>
+        <v>200</v>
+      </c>
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="77"/>
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="89"/>
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
-      <c r="G46" s="74"/>
+      <c r="A46" s="67"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="69"/>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="90"/>
-      <c r="B47" s="69"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="82"/>
+      <c r="A47" s="70"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="71"/>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="91"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="92"/>
-      <c r="E48" s="92"/>
-      <c r="F48" s="92"/>
-      <c r="G48" s="93"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="73"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="74"/>
     </row>
     <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="94" t="s">
+      <c r="A49" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="73"/>
-      <c r="C49" s="95"/>
-      <c r="D49" s="70" t="s">
+      <c r="B49" s="68"/>
+      <c r="C49" s="87"/>
+      <c r="D49" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="E49" s="72" t="str">
+      <c r="E49" s="105" t="str">
         <f>IF(G44&lt;100,"Tidak teridentifikasi",IF(G44&gt;=100,"CERDAS ISTIMEWA"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F49" s="73"/>
-      <c r="G49" s="74"/>
+      <c r="F49" s="68"/>
+      <c r="G49" s="69"/>
     </row>
     <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="96"/>
-      <c r="B50" s="76"/>
-      <c r="C50" s="97"/>
-      <c r="D50" s="71"/>
-      <c r="E50" s="75"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="77"/>
+      <c r="A50" s="88"/>
+      <c r="B50" s="89"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="104"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="89"/>
+      <c r="G50" s="107"/>
     </row>
     <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14137,6 +14137,11 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="D49:D50"/>
@@ -14148,11 +14153,6 @@
     <mergeCell ref="A45:G45"/>
     <mergeCell ref="A46:G48"/>
     <mergeCell ref="A49:C50"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -14172,15 +14172,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -14198,11 +14198,11 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -14211,11 +14211,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -14224,11 +14224,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -14237,11 +14237,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -14250,11 +14250,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -14263,11 +14263,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -14276,11 +14276,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -14331,7 +14331,7 @@
       <c r="G13" s="3"/>
     </row>
     <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="106" t="s">
+      <c r="A16" s="102" t="s">
         <v>48</v>
       </c>
       <c r="B16" s="79"/>
@@ -14353,24 +14353,24 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="93"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="74"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="107"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="82"/>
+      <c r="A19" s="97"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="71"/>
     </row>
     <row r="20" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
@@ -14396,7 +14396,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="108" t="s">
+      <c r="A21" s="98" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="28">
@@ -14420,7 +14420,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="28">
         <v>2</v>
       </c>
@@ -14442,7 +14442,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="99" t="s">
         <v>54</v>
       </c>
       <c r="B23" s="28">
@@ -14466,7 +14466,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
+      <c r="A24" s="83"/>
       <c r="B24" s="28">
         <v>2</v>
       </c>
@@ -14488,7 +14488,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="28">
         <v>3</v>
       </c>
@@ -14510,7 +14510,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
+      <c r="A26" s="83"/>
       <c r="B26" s="28">
         <v>4</v>
       </c>
@@ -14532,7 +14532,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
+      <c r="A27" s="83"/>
       <c r="B27" s="28">
         <v>5</v>
       </c>
@@ -14554,7 +14554,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="28">
         <v>6</v>
       </c>
@@ -14576,7 +14576,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="28">
         <v>7</v>
       </c>
@@ -14630,79 +14630,79 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="101" t="s">
+      <c r="A32" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="88"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="77"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="74"/>
+      <c r="A33" s="67"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="69"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="90"/>
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="82"/>
+      <c r="A34" s="70"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="66"/>
+      <c r="G34" s="71"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="91"/>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="93"/>
+      <c r="A35" s="72"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="74"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="94" t="s">
+      <c r="A36" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="73"/>
-      <c r="C36" s="95"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="87"/>
       <c r="D36" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E36" s="98" t="str">
+      <c r="E36" s="75" t="str">
         <f>IF(G30&lt;100,"Tidak teridentifikasi",IF(G30&gt;=100,"Tunarungu berat/menyeluruh"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F36" s="87"/>
-      <c r="G36" s="88"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="77"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="96"/>
-      <c r="B37" s="76"/>
-      <c r="C37" s="97"/>
+      <c r="A37" s="88"/>
+      <c r="B37" s="89"/>
+      <c r="C37" s="90"/>
       <c r="D37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="103" t="str">
+      <c r="E37" s="91" t="str">
         <f>IF(G31&lt;100,"Tidak teridentifikasi",IF(G31&gt;=100,"Tunarungu sebagian"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F37" s="104"/>
-      <c r="G37" s="105"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="93"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="69"/>
+      <c r="D38" s="100"/>
+      <c r="E38" s="66"/>
       <c r="F38" s="5"/>
       <c r="G38" s="1"/>
     </row>
@@ -14737,19 +14737,19 @@
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="110"/>
-      <c r="E66" s="69"/>
-      <c r="F66" s="110"/>
-      <c r="G66" s="69"/>
+      <c r="D66" s="100"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="100"/>
+      <c r="G66" s="66"/>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="110"/>
-      <c r="E67" s="69"/>
-      <c r="F67" s="110"/>
-      <c r="G67" s="69"/>
+      <c r="D67" s="100"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="100"/>
+      <c r="G67" s="66"/>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15686,6 +15686,16 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A23:A29"/>
@@ -15699,16 +15709,6 @@
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="D66:E66"/>
     <mergeCell ref="F66:G66"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -15728,15 +15728,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -15754,11 +15754,11 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -15767,11 +15767,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -15780,11 +15780,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -15793,11 +15793,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -15806,11 +15806,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -15819,11 +15819,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -15832,11 +15832,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -15918,15 +15918,15 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="93"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="74"/>
     </row>
     <row r="19" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
@@ -15952,7 +15952,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="108" t="str">
+      <c r="A20" s="98" t="str">
         <f>A16</f>
         <v>IDENTIFIKASI HAMBATAN INTELEKTUAL KATEGORI TUNAGRAHITA</v>
       </c>
@@ -15977,7 +15977,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="20">
         <v>2</v>
       </c>
@@ -15999,7 +15999,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
+      <c r="A22" s="83"/>
       <c r="B22" s="20">
         <v>3</v>
       </c>
@@ -16021,7 +16021,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="20">
         <v>4</v>
       </c>
@@ -16043,7 +16043,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
+      <c r="A24" s="83"/>
       <c r="B24" s="20">
         <v>5</v>
       </c>
@@ -16065,7 +16065,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="20">
         <v>6</v>
       </c>
@@ -16088,7 +16088,7 @@
       <c r="H25" s="38"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
+      <c r="A26" s="83"/>
       <c r="B26" s="20">
         <v>7</v>
       </c>
@@ -16110,7 +16110,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
+      <c r="A27" s="83"/>
       <c r="B27" s="20">
         <v>8</v>
       </c>
@@ -16132,7 +16132,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="20">
         <v>9</v>
       </c>
@@ -16154,7 +16154,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
+      <c r="A29" s="83"/>
       <c r="B29" s="20">
         <v>10</v>
       </c>
@@ -16176,7 +16176,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
+      <c r="A30" s="83"/>
       <c r="B30" s="20">
         <v>11</v>
       </c>
@@ -16198,7 +16198,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="84"/>
+      <c r="A31" s="83"/>
       <c r="B31" s="20">
         <v>12</v>
       </c>
@@ -16220,7 +16220,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="84"/>
+      <c r="A32" s="83"/>
       <c r="B32" s="20">
         <v>13</v>
       </c>
@@ -16242,7 +16242,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="84"/>
+      <c r="A33" s="83"/>
       <c r="B33" s="20">
         <v>14</v>
       </c>
@@ -16264,7 +16264,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="84"/>
+      <c r="A34" s="83"/>
       <c r="B34" s="20">
         <v>15</v>
       </c>
@@ -16286,7 +16286,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="85"/>
+      <c r="A35" s="84"/>
       <c r="B35" s="20">
         <v>16</v>
       </c>
@@ -16322,68 +16322,68 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="101" t="s">
+      <c r="A37" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="87"/>
-      <c r="C37" s="87"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="87"/>
-      <c r="F37" s="87"/>
-      <c r="G37" s="88"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="77"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="89"/>
-      <c r="B38" s="73"/>
-      <c r="C38" s="73"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="73"/>
-      <c r="G38" s="74"/>
+      <c r="A38" s="67"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="69"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="90"/>
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="82"/>
+      <c r="A39" s="70"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="71"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="91"/>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="93"/>
+      <c r="A40" s="72"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="94" t="s">
+      <c r="A41" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="73"/>
-      <c r="C41" s="95"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="87"/>
       <c r="D41" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="E41" s="98" t="str">
+      <c r="E41" s="75" t="str">
         <f>IF(G36&lt;100,"Tidak teridentifikasi",IF(G36&gt;=100,"Tunagrahita"))</f>
         <v>Tunagrahita</v>
       </c>
-      <c r="F41" s="87"/>
-      <c r="G41" s="88"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="77"/>
       <c r="H41" s="38"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="96"/>
-      <c r="B42" s="76"/>
-      <c r="C42" s="97"/>
+      <c r="A42" s="88"/>
+      <c r="B42" s="89"/>
+      <c r="C42" s="90"/>
       <c r="D42" s="21"/>
-      <c r="E42" s="103"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="105"/>
+      <c r="E42" s="91"/>
+      <c r="F42" s="92"/>
+      <c r="G42" s="93"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -17345,6 +17345,11 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="E41:G41"/>
@@ -17356,11 +17361,6 @@
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A38:G40"/>
     <mergeCell ref="A41:C42"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -17383,15 +17383,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -17409,11 +17409,11 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -17422,11 +17422,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -17435,11 +17435,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -17448,11 +17448,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -17461,11 +17461,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -17474,11 +17474,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -17487,11 +17487,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -17565,24 +17565,24 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="82"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="71"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
       <c r="B18" s="1"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="82"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="71"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
@@ -17608,7 +17608,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="108" t="str">
+      <c r="A20" s="98" t="str">
         <f>A15</f>
         <v>IDENTIFIKASI HAMBATAN FISIK MOTORIK</v>
       </c>
@@ -17633,7 +17633,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="28">
         <v>2</v>
       </c>
@@ -17655,7 +17655,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
+      <c r="A22" s="83"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
@@ -17677,7 +17677,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="28">
         <v>4</v>
       </c>
@@ -17699,7 +17699,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="28">
         <v>5</v>
       </c>
@@ -17735,67 +17735,67 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="101" t="s">
+      <c r="A26" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="87"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="88"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="77"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="89"/>
-      <c r="B27" s="73"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="74"/>
+      <c r="A27" s="67"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="69"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="90"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="82"/>
+      <c r="A28" s="70"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="71"/>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="91"/>
-      <c r="B29" s="92"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="93"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="74"/>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="94" t="s">
+      <c r="A30" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="73"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="70" t="s">
+      <c r="B30" s="68"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="E30" s="72" t="str">
+      <c r="E30" s="105" t="str">
         <f>IF(G25&lt;100,"Tidak teridentifikasi",IF(G25&gt;=100,"Tunadaksa"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F30" s="73"/>
-      <c r="G30" s="74"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="69"/>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="96"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="77"/>
+      <c r="A31" s="88"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="107"/>
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -18768,6 +18768,11 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A27:G29"/>
@@ -18781,11 +18786,6 @@
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="A20:A24"/>
     <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -18808,15 +18808,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -18834,11 +18834,11 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -18847,11 +18847,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -18860,11 +18860,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -18873,11 +18873,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -18886,11 +18886,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -18899,11 +18899,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -18912,11 +18912,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -18990,15 +18990,15 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="82"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="71"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
@@ -19033,7 +19033,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="109" t="s">
         <v>95</v>
       </c>
       <c r="B20" s="28">
@@ -19057,7 +19057,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="28">
         <v>2</v>
       </c>
@@ -19079,7 +19079,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
+      <c r="A22" s="83"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
@@ -19101,7 +19101,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="28">
         <v>4</v>
       </c>
@@ -19123,7 +19123,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
+      <c r="A24" s="83"/>
       <c r="B24" s="28">
         <v>5</v>
       </c>
@@ -19145,7 +19145,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="28">
         <v>6</v>
       </c>
@@ -19167,7 +19167,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
+      <c r="A26" s="83"/>
       <c r="B26" s="28">
         <v>7</v>
       </c>
@@ -19189,7 +19189,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
+      <c r="A27" s="83"/>
       <c r="B27" s="28">
         <v>8</v>
       </c>
@@ -19211,7 +19211,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="28">
         <v>9</v>
       </c>
@@ -19233,7 +19233,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="53"/>
       <c r="C29" s="54" t="s">
         <v>83</v>
@@ -19247,67 +19247,67 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="86" t="s">
+      <c r="A30" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="87"/>
-      <c r="C30" s="87"/>
-      <c r="D30" s="87"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="87"/>
-      <c r="G30" s="88"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="77"/>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="89"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="74"/>
+      <c r="A31" s="67"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="69"/>
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="90"/>
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="82"/>
+      <c r="A32" s="70"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="66"/>
+      <c r="G32" s="71"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="92"/>
-      <c r="G33" s="93"/>
+      <c r="A33" s="72"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="94" t="s">
+      <c r="A34" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="73"/>
-      <c r="C34" s="95"/>
-      <c r="D34" s="70" t="s">
+      <c r="B34" s="68"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="72" t="str">
+      <c r="E34" s="105" t="str">
         <f>IF(G29&lt;100,"Tidak teridentifikasi",IF(G29&gt;=100,"Tunalaras"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F34" s="73"/>
-      <c r="G34" s="74"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="69"/>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="96"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="97"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="77"/>
+      <c r="A35" s="88"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="107"/>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20276,6 +20276,11 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="D34:D35"/>
@@ -20287,11 +20292,6 @@
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A31:G33"/>
     <mergeCell ref="A34:C35"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -20314,15 +20314,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -20340,11 +20340,11 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -20353,11 +20353,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -20366,11 +20366,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -20379,11 +20379,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -20392,11 +20392,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -20405,11 +20405,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -20418,11 +20418,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -20496,15 +20496,15 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="82"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="71"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
@@ -20539,14 +20539,14 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="109" t="s">
         <v>108</v>
       </c>
       <c r="B20" s="28">
         <v>1</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="D20" s="35">
         <v>20</v>
@@ -20563,12 +20563,12 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="28">
         <v>2</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" s="35">
         <v>10</v>
@@ -20586,12 +20586,12 @@
       <c r="H21" s="38"/>
     </row>
     <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
+      <c r="A22" s="83"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D22" s="35">
         <v>10</v>
@@ -20609,12 +20609,12 @@
       <c r="H22" s="38"/>
     </row>
     <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="28">
         <v>4</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D23" s="35">
         <v>20</v>
@@ -20632,12 +20632,12 @@
       <c r="H23" s="38"/>
     </row>
     <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
+      <c r="A24" s="83"/>
       <c r="B24" s="28">
         <v>5</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D24" s="35">
         <v>10</v>
@@ -20655,12 +20655,12 @@
       <c r="H24" s="38"/>
     </row>
     <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="28">
         <v>6</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D25" s="35">
         <v>20</v>
@@ -20678,12 +20678,12 @@
       <c r="H25" s="38"/>
     </row>
     <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
+      <c r="A26" s="83"/>
       <c r="B26" s="28">
         <v>7</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26" s="35">
         <v>10</v>
@@ -20701,12 +20701,12 @@
       <c r="H26" s="38"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
+      <c r="A27" s="83"/>
       <c r="B27" s="28">
         <v>8</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D27" s="35">
         <v>10</v>
@@ -20724,12 +20724,12 @@
       <c r="H27" s="38"/>
     </row>
     <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="28">
         <v>9</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>117</v>
+        <v>202</v>
       </c>
       <c r="D28" s="35">
         <v>20</v>
@@ -20747,12 +20747,12 @@
       <c r="H28" s="38"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
+      <c r="A29" s="83"/>
       <c r="B29" s="28">
         <v>10</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D29" s="35">
         <v>20</v>
@@ -20770,12 +20770,12 @@
       <c r="H29" s="38"/>
     </row>
     <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
+      <c r="A30" s="83"/>
       <c r="B30" s="28">
         <v>11</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D30" s="35">
         <v>10</v>
@@ -20793,12 +20793,12 @@
       <c r="H30" s="38"/>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="84"/>
+      <c r="A31" s="83"/>
       <c r="B31" s="28">
         <v>12</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D31" s="35">
         <v>20</v>
@@ -20815,12 +20815,12 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
+      <c r="A32" s="84"/>
       <c r="B32" s="28">
         <v>13</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D32" s="35">
         <v>10</v>
@@ -20853,66 +20853,66 @@
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="113" t="s">
-        <v>122</v>
-      </c>
-      <c r="B34" s="87"/>
-      <c r="C34" s="87"/>
-      <c r="D34" s="87"/>
-      <c r="E34" s="87"/>
-      <c r="F34" s="87"/>
-      <c r="G34" s="88"/>
+        <v>120</v>
+      </c>
+      <c r="B34" s="76"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="77"/>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="89"/>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="74"/>
+      <c r="A35" s="67"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="69"/>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="90"/>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="82"/>
+      <c r="A36" s="70"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="71"/>
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="91"/>
-      <c r="B37" s="92"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="93"/>
+      <c r="A37" s="72"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="94" t="s">
+      <c r="A38" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="73"/>
-      <c r="C38" s="95"/>
-      <c r="D38" s="70" t="s">
+      <c r="B38" s="68"/>
+      <c r="C38" s="87"/>
+      <c r="D38" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="E38" s="72" t="str">
+      <c r="E38" s="105" t="str">
         <f>IF(G33&lt;100,"Tidak teridentifikasi",IF(G33&gt;=100,"AUTIS"))</f>
         <v>AUTIS</v>
       </c>
-      <c r="F38" s="73"/>
-      <c r="G38" s="74"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="69"/>
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="91"/>
-      <c r="B39" s="92"/>
+      <c r="A39" s="72"/>
+      <c r="B39" s="73"/>
       <c r="C39" s="114"/>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
-      <c r="F39" s="92"/>
-      <c r="G39" s="93"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -21877,6 +21877,11 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="D38:D39"/>
@@ -21888,11 +21893,6 @@
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="A35:G37"/>
     <mergeCell ref="A38:C39"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -21916,15 +21916,15 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="96"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -21942,11 +21942,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -21955,11 +21955,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -21968,11 +21968,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -21981,11 +21981,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -21994,11 +21994,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -22007,11 +22007,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -22020,11 +22020,11 @@
       <c r="B10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
     </row>
     <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
@@ -22077,7 +22077,7 @@
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="115" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B16" s="79"/>
       <c r="C16" s="79"/>
@@ -22098,15 +22098,15 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="81" t="s">
+      <c r="A18" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="69"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="82"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="71"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
@@ -22134,7 +22134,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G20" s="59" t="s">
         <v>50</v>
@@ -22142,13 +22142,13 @@
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="116" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B21" s="28">
         <v>1</v>
       </c>
       <c r="C21" s="60" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D21" s="35">
         <v>10</v>
@@ -22165,12 +22165,12 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="90"/>
+      <c r="A22" s="70"/>
       <c r="B22" s="28">
         <v>2</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D22" s="35">
         <v>17</v>
@@ -22187,12 +22187,12 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="90"/>
+      <c r="A23" s="70"/>
       <c r="B23" s="28">
         <v>3</v>
       </c>
       <c r="C23" s="60" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D23" s="35">
         <v>17</v>
@@ -22209,12 +22209,12 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="90"/>
+      <c r="A24" s="70"/>
       <c r="B24" s="28">
         <v>4</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D24" s="35">
         <v>17</v>
@@ -22231,12 +22231,12 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="90"/>
+      <c r="A25" s="70"/>
       <c r="B25" s="28">
         <v>5</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D25" s="35">
         <v>17</v>
@@ -22253,12 +22253,12 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="90"/>
+      <c r="A26" s="70"/>
       <c r="B26" s="28">
         <v>6</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D26" s="35">
         <v>17</v>
@@ -22275,12 +22275,12 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="90"/>
+      <c r="A27" s="70"/>
       <c r="B27" s="28">
         <v>7</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D27" s="35">
         <v>17</v>
@@ -22297,12 +22297,12 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="90"/>
+      <c r="A28" s="70"/>
       <c r="B28" s="28">
         <v>8</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D28" s="35">
         <v>17</v>
@@ -22319,12 +22319,12 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="90"/>
+      <c r="A29" s="70"/>
       <c r="B29" s="28">
         <v>9</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D29" s="35">
         <v>17</v>
@@ -22341,12 +22341,12 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="90"/>
+      <c r="A30" s="70"/>
       <c r="B30" s="28">
         <v>10</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D30" s="35">
         <v>17</v>
@@ -22363,12 +22363,12 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="90"/>
+      <c r="A31" s="70"/>
       <c r="B31" s="28">
         <v>11</v>
       </c>
       <c r="C31" s="60" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D31" s="35">
         <v>17</v>
@@ -22385,12 +22385,12 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="90"/>
+      <c r="A32" s="70"/>
       <c r="B32" s="28">
         <v>12</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D32" s="35">
         <v>17</v>
@@ -22407,12 +22407,12 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="90"/>
+      <c r="A33" s="70"/>
       <c r="B33" s="28">
         <v>13</v>
       </c>
       <c r="C33" s="60" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D33" s="35">
         <v>17</v>
@@ -22429,12 +22429,12 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="90"/>
+      <c r="A34" s="70"/>
       <c r="B34" s="28">
         <v>14</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D34" s="35">
         <v>17</v>
@@ -22451,12 +22451,12 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="90"/>
+      <c r="A35" s="70"/>
       <c r="B35" s="28">
         <v>15</v>
       </c>
       <c r="C35" s="60" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D35" s="35">
         <v>17</v>
@@ -22473,12 +22473,12 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="90"/>
+      <c r="A36" s="70"/>
       <c r="B36" s="28">
         <v>16</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D36" s="35">
         <v>17</v>
@@ -22495,12 +22495,12 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="90"/>
+      <c r="A37" s="70"/>
       <c r="B37" s="28">
         <v>17</v>
       </c>
       <c r="C37" s="60" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D37" s="35">
         <v>17</v>
@@ -22517,12 +22517,12 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="90"/>
+      <c r="A38" s="70"/>
       <c r="B38" s="28">
         <v>18</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D38" s="35">
         <v>17</v>
@@ -22554,66 +22554,66 @@
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="113" t="s">
-        <v>144</v>
-      </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="87"/>
-      <c r="G40" s="88"/>
+        <v>142</v>
+      </c>
+      <c r="B40" s="76"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="77"/>
     </row>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="89"/>
-      <c r="B41" s="73"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="74"/>
+      <c r="A41" s="67"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="69"/>
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="90"/>
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="82"/>
+      <c r="A42" s="70"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="71"/>
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="91"/>
-      <c r="B43" s="92"/>
-      <c r="C43" s="92"/>
-      <c r="D43" s="92"/>
-      <c r="E43" s="92"/>
-      <c r="F43" s="92"/>
-      <c r="G43" s="93"/>
+      <c r="A43" s="72"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="73"/>
+      <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="94" t="s">
+      <c r="A44" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="73"/>
-      <c r="C44" s="95"/>
-      <c r="D44" s="70" t="s">
+      <c r="B44" s="68"/>
+      <c r="C44" s="87"/>
+      <c r="D44" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="E44" s="72" t="str">
+      <c r="E44" s="105" t="str">
         <f>IF(G39&lt;100,"Tidak teridentifikasi",IF(G39&gt;=100,"ADHD/HIPERAKTIF"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F44" s="73"/>
-      <c r="G44" s="74"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="69"/>
     </row>
     <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="96"/>
-      <c r="B45" s="76"/>
-      <c r="C45" s="97"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="75"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="77"/>
+      <c r="A45" s="88"/>
+      <c r="B45" s="89"/>
+      <c r="C45" s="90"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="106"/>
+      <c r="F45" s="89"/>
+      <c r="G45" s="107"/>
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -23572,6 +23572,11 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="D44:D45"/>
@@ -23583,11 +23588,6 @@
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A41:G43"/>
     <mergeCell ref="A44:C45"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -23611,15 +23611,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -23637,11 +23637,11 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -23650,11 +23650,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -23663,11 +23663,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -23676,11 +23676,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -23689,11 +23689,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -23702,11 +23702,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -23715,11 +23715,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -23772,7 +23772,7 @@
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="78" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B15" s="79"/>
       <c r="C15" s="79"/>
@@ -23802,15 +23802,15 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="93"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="74"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
@@ -23844,7 +23844,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D20" s="9">
         <v>20</v>
@@ -23866,7 +23866,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D21" s="9">
         <v>30</v>
@@ -23888,7 +23888,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D22" s="9">
         <v>30</v>
@@ -23910,7 +23910,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D23" s="9">
         <v>30</v>
@@ -23932,7 +23932,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D24" s="9">
         <v>30</v>
@@ -23954,7 +23954,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D25" s="9">
         <v>30</v>
@@ -23976,7 +23976,7 @@
         <v>7</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D26" s="9">
         <v>30</v>
@@ -23998,7 +23998,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D27" s="9">
         <v>30</v>
@@ -24020,7 +24020,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D28" s="9">
         <v>30</v>
@@ -24042,7 +24042,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="61" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D29" s="9">
         <v>30</v>
@@ -24074,66 +24074,66 @@
     </row>
     <row r="31" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="119" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="87"/>
-      <c r="C31" s="87"/>
-      <c r="D31" s="87"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="87"/>
-      <c r="G31" s="88"/>
+        <v>154</v>
+      </c>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="77"/>
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="89"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="74"/>
+      <c r="A32" s="67"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="69"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="90"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="82"/>
+      <c r="A33" s="70"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="71"/>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="92"/>
-      <c r="G34" s="93"/>
+      <c r="A34" s="72"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="74"/>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="94" t="s">
+      <c r="A35" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="73"/>
-      <c r="C35" s="95"/>
-      <c r="D35" s="70" t="s">
+      <c r="B35" s="68"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="E35" s="72" t="str">
+      <c r="E35" s="105" t="str">
         <f>IF(G30&lt;100,"Tidak teridentifikasi",IF(G30&gt;=100,"SLOW LEARNER/LAMBAN BELAJAR"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F35" s="73"/>
-      <c r="G35" s="74"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="69"/>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="96"/>
-      <c r="B36" s="76"/>
-      <c r="C36" s="97"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="77"/>
+      <c r="A36" s="88"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="104"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="107"/>
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -25101,6 +25101,11 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="D35:D36"/>
@@ -25112,11 +25117,6 @@
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A32:G34"/>
     <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -25140,15 +25140,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -25166,11 +25166,11 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -25179,11 +25179,11 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -25192,11 +25192,11 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -25205,11 +25205,11 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -25218,11 +25218,11 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -25231,11 +25231,11 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -25244,11 +25244,11 @@
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -25309,7 +25309,7 @@
     </row>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="78" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B15" s="79"/>
       <c r="C15" s="79"/>
@@ -25330,24 +25330,24 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="82"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="71"/>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="99"/>
-      <c r="B18" s="92"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="93"/>
+      <c r="A18" s="81"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="74"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="51" t="s">
@@ -25373,14 +25373,14 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="100" t="s">
-        <v>158</v>
+      <c r="A20" s="82" t="s">
+        <v>156</v>
       </c>
       <c r="B20" s="28">
         <v>1</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D20" s="35">
         <v>50</v>
@@ -25397,12 +25397,12 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="28">
         <v>2</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D21" s="35">
         <v>50</v>
@@ -25419,12 +25419,12 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D22" s="35">
         <v>50</v>
@@ -25441,14 +25441,14 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="100" t="s">
-        <v>162</v>
+      <c r="A23" s="82" t="s">
+        <v>160</v>
       </c>
       <c r="B23" s="28">
         <v>1</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D23" s="35">
         <v>50</v>
@@ -25465,12 +25465,12 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
+      <c r="A24" s="83"/>
       <c r="B24" s="28">
         <v>2</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D24" s="35">
         <v>50</v>
@@ -25487,12 +25487,12 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="28">
         <v>3</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D25" s="35">
         <v>50</v>
@@ -25509,12 +25509,12 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="28">
         <v>4</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D26" s="35">
         <v>50</v>
@@ -25532,13 +25532,13 @@
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="121" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B27" s="28">
         <v>1</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D27" s="35">
         <v>50</v>
@@ -25555,12 +25555,12 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="28">
         <v>2</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D28" s="35">
         <v>50</v>
@@ -25577,12 +25577,12 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
+      <c r="A29" s="83"/>
       <c r="B29" s="28">
         <v>3</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D29" s="35">
         <v>50</v>
@@ -25599,12 +25599,12 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
+      <c r="A30" s="83"/>
       <c r="B30" s="28">
         <v>4</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D30" s="35">
         <v>50</v>
@@ -25621,12 +25621,12 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="28">
         <v>5</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D31" s="35">
         <v>50</v>
@@ -25644,41 +25644,41 @@
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="113" t="s">
-        <v>173</v>
-      </c>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="88"/>
+        <v>171</v>
+      </c>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="77"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="74"/>
+      <c r="A33" s="67"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="69"/>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="90"/>
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="82"/>
+      <c r="A34" s="70"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="66"/>
+      <c r="G34" s="71"/>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="91"/>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="93"/>
+      <c r="A35" s="72"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="74"/>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44"/>
@@ -25712,7 +25712,7 @@
       <c r="A38" s="44"/>
       <c r="B38" s="1"/>
       <c r="C38" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
@@ -25723,48 +25723,48 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="94" t="s">
+      <c r="A39" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="73"/>
-      <c r="C39" s="95"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="87"/>
       <c r="D39" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E39" s="98" t="str">
+      <c r="E39" s="75" t="str">
         <f>IF(G36&lt;100,"Tidak teridentifikasi",IF(G36&gt;=100,"DISKLEKSIA"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F39" s="87"/>
-      <c r="G39" s="88"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="77"/>
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="90"/>
-      <c r="B40" s="69"/>
+      <c r="A40" s="70"/>
+      <c r="B40" s="66"/>
       <c r="C40" s="120"/>
       <c r="D40" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="98" t="str">
+      <c r="E40" s="75" t="str">
         <f>IF(G37&lt;100,"Tidak teridentifikasi",IF(G37&gt;=100,"DISGRAFIA"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F40" s="87"/>
-      <c r="G40" s="88"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="77"/>
     </row>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="96"/>
-      <c r="B41" s="76"/>
-      <c r="C41" s="97"/>
+      <c r="A41" s="88"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="90"/>
       <c r="D41" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="E41" s="103" t="str">
+        <v>173</v>
+      </c>
+      <c r="E41" s="91" t="str">
         <f>IF(G38&lt;100,"Tidak teridentifikasi",IF(G38&gt;=100,"DISKALKULIA"))</f>
         <v>Tidak teridentifikasi</v>
       </c>
-      <c r="F41" s="104"/>
-      <c r="G41" s="105"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="93"/>
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -26727,6 +26727,11 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A32:G32"/>
@@ -26742,11 +26747,6 @@
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
